--- a/workdata.xlsx
+++ b/workdata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwcon\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwcon\Desktop\JIKKENBA\matsu-26bd-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB39148-5FC0-4052-AFC9-3122CAFAA926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B15D2DB-CD93-430D-A832-3468C948D972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="5625" windowWidth="21600" windowHeight="11835" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="博客" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="624">
   <si>
     <t>序号</t>
   </si>
@@ -1965,6 +1965,9 @@
       </rPr>
       <t>https://mantan-web.jp/article/20260117dog00m200022000c.html</t>
     </r>
+  </si>
+  <si>
+    <t>谷口愛季</t>
   </si>
 </sst>
 </file>
@@ -2355,14 +2358,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="博客"/>
   <dimension ref="A1:G85"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.61328125" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="38.53515625" customWidth="1"/>
-    <col min="6" max="6" width="10.3828125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="67.07421875" customWidth="1"/>
+    <col min="5" max="5" width="38.5546875" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="67.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" ht="18" customHeight="1">
@@ -3262,7 +3265,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="28">
+    <row r="40" spans="1:7" ht="28.5">
       <c r="A40" s="12">
         <v>39</v>
       </c>
@@ -4329,10 +4332,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="樱坂频道"/>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.07421875" customWidth="1"/>
-    <col min="3" max="3" width="93.07421875" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" customWidth="1"/>
+    <col min="3" max="3" width="93.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1">
@@ -4469,9 +4472,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="官方抖音"/>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.84375" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" customWidth="1"/>
     <col min="3" max="3" width="56" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4750,11 +4753,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="CD收录"/>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.07421875" customWidth="1"/>
-    <col min="3" max="3" width="56.765625" customWidth="1"/>
-    <col min="4" max="4" width="38.4609375" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" customWidth="1"/>
+    <col min="3" max="3" width="56.77734375" customWidth="1"/>
+    <col min="4" max="4" width="38.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
@@ -4953,11 +4956,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="握手会"/>
   <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.3828125" customWidth="1"/>
-    <col min="3" max="3" width="79.53515625" customWidth="1"/>
-    <col min="4" max="4" width="20.61328125" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="79.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
@@ -5397,7 +5400,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="18.5">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5411,7 +5414,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="18.5">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5428,7 +5431,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="18.5">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5482,11 +5485,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="出演综艺"/>
   <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.07421875" customWidth="1"/>
-    <col min="4" max="4" width="37.61328125" customWidth="1"/>
-    <col min="5" max="5" width="58.53515625" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" customWidth="1"/>
+    <col min="4" max="4" width="37.6640625" customWidth="1"/>
+    <col min="5" max="5" width="58.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
@@ -6011,13 +6014,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="出席活动"/>
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.07421875" customWidth="1"/>
-    <col min="2" max="2" width="12.53515625" customWidth="1"/>
-    <col min="3" max="3" width="21.15234375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="76.23046875" customWidth="1"/>
-    <col min="5" max="5" width="52.4609375" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="76.21875" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1">
@@ -6320,12 +6323,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="转樱"/>
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.15234375" customWidth="1"/>
-    <col min="2" max="2" width="11.61328125" customWidth="1"/>
-    <col min="3" max="3" width="7.69140625" customWidth="1"/>
-    <col min="4" max="4" width="49.61328125" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" customWidth="1"/>
+    <col min="4" max="4" width="49.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
@@ -7065,13 +7068,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="广播"/>
-  <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.23046875" customWidth="1"/>
+    <col min="1" max="1" width="6.21875" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="27.23046875" customWidth="1"/>
-    <col min="5" max="5" width="27.07421875" customWidth="1"/>
+    <col min="4" max="4" width="27.21875" customWidth="1"/>
+    <col min="5" max="5" width="27.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
@@ -7513,6 +7516,68 @@
       </c>
       <c r="E30" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="18" customHeight="1">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>20261006</v>
+      </c>
+      <c r="C31">
+        <v>615</v>
+      </c>
+      <c r="D31" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="18" customHeight="1">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>20261006</v>
+      </c>
+      <c r="C32">
+        <v>616</v>
+      </c>
+      <c r="D32" t="s">
+        <v>87</v>
+      </c>
+      <c r="E32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="18" customHeight="1">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>20261003</v>
+      </c>
+      <c r="D33" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="18" customHeight="1">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>20261010</v>
+      </c>
+      <c r="D34" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" t="s">
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -7524,11 +7589,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="杂志报刊"/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.4609375" customWidth="1"/>
-    <col min="3" max="3" width="40.15234375" customWidth="1"/>
-    <col min="5" max="5" width="44.23046875" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" customWidth="1"/>
+    <col min="3" max="3" width="40.109375" customWidth="1"/>
+    <col min="5" max="5" width="44.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1">
@@ -7699,13 +7764,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="网媒采访"/>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.61328125" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="76.765625" customWidth="1"/>
-    <col min="5" max="5" width="28.765625" customWidth="1"/>
-    <col min="6" max="6" width="90.765625" customWidth="1"/>
+    <col min="4" max="4" width="76.77734375" customWidth="1"/>
+    <col min="5" max="5" width="28.77734375" customWidth="1"/>
+    <col min="6" max="6" width="90.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1">
@@ -7947,11 +8012,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="LIVE演出"/>
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="5" width="57.3046875" customWidth="1"/>
+    <col min="5" max="5" width="57.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1">
@@ -8446,7 +8511,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18.5">
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>27</v>
       </c>
@@ -8466,7 +8531,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="18.5">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8495,11 +8560,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="音番打歌"/>
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="14.15234375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.69140625" customWidth="1"/>
-    <col min="4" max="4" width="28.15234375" customWidth="1"/>
-    <col min="5" max="5" width="25.61328125" customWidth="1"/>
+    <col min="1" max="1" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="28.109375" customWidth="1"/>
+    <col min="5" max="5" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1">
